--- a/data/trans_orig/IP11C$ingresado-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP11C$ingresado-Clase-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -944,112 +944,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1695</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5305</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>68,16%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>28,94%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3965</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>31,84%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>67,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -1057,112 +1057,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -1400,42 +1400,42 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,67 +1445,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>445</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -1513,42 +1513,42 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1558,67 +1558,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1856,17 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1891,77 +1891,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -1969,112 +1969,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -2312,112 +2312,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -2425,112 +2425,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -2768,112 +2768,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -2881,112 +2881,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>599</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>599</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3299,37 +3299,37 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3377,72 +3377,72 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -3680,112 +3680,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>25254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>28958</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>49791</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>43070</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>56153</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -3793,112 +3793,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>14365</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>28958</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23185</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>49791</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>42345</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>56512</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -4370,112 +4370,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -4483,112 +4483,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>37,29%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>68,26%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5597</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7622</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>62,71%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>31,6%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>85,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -4826,112 +4826,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -4939,112 +4939,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -5282,112 +5282,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -5395,112 +5395,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2782</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4874</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>44,64%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11,47%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>52,13%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>5556</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>55,36%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>21,77%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>89,15%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2626</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>77,81%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5748,102 +5748,102 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5861,102 +5861,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -6194,112 +6194,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -6307,112 +6307,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -6650,17 +6650,17 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>695</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -6690,37 +6690,37 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -6763,17 +6763,17 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -6803,37 +6803,37 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6843,32 +6843,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15274</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7106,112 +7106,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>24066</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>33680</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25531</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>64586</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>55595</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48047</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -7219,112 +7219,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24066</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>26688</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>12881</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>24564</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>34,38%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>40520</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>33744</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>47105</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>56,71%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>65,93%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>55655</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73195</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -7796,17 +7796,17 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -7871,37 +7871,37 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -7909,17 +7909,17 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7934,87 +7934,87 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1373</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -8252,17 +8252,17 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -8292,72 +8292,72 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -8365,17 +8365,17 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -8405,72 +8405,72 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -8708,17 +8708,17 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -8748,72 +8748,72 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -8821,112 +8821,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>737</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>737</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -9164,112 +9164,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -9277,112 +9277,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -9620,112 +9620,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -9733,112 +9733,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>818</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -10076,17 +10076,17 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -10189,17 +10189,17 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -10264,12 +10264,12 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>472</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -10532,112 +10532,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>54793</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -10645,112 +10645,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19644</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34505</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>44297</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>55181</t>
+          <t>12821</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -11222,112 +11222,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -11335,112 +11335,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -11678,112 +11678,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>810</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -11791,112 +11791,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12134,17 +12134,17 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>735</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -12247,17 +12247,17 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -12590,112 +12590,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -12703,112 +12703,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>877</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -13046,17 +13046,17 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -13086,72 +13086,72 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>903</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -13159,17 +13159,17 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -13199,72 +13199,72 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13502,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -13577,37 +13577,37 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -13615,7 +13615,7 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -13655,12 +13655,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -13690,37 +13690,37 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>398</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -13958,112 +13958,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -14071,112 +14071,112 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>2291</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35922</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
